--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:17</t>
+    <t xml:space="preserve">2026-09-09 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:13</t>
+    <t xml:space="preserve">2026-09-17 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:09</t>
+    <t xml:space="preserve">2026-09-23 12:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:38</t>
+    <t xml:space="preserve">2026-10-02 14:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:18</t>
+    <t xml:space="preserve">2026-10-04 09:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:06</t>
+    <t xml:space="preserve">2026-10-05 11:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -677,7 +677,7 @@
         <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>475602.12</v>
+        <v>475602.13</v>
       </c>
     </row>
     <row r="8">
@@ -745,7 +745,7 @@
         <v>2024</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>409024.62</v>
+        <v>409024.63</v>
       </c>
     </row>
     <row r="12">
